--- a/model_implementation/data/full_railway_simulation.xlsx
+++ b/model_implementation/data/full_railway_simulation.xlsx
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14.55</v>
+        <v>12</v>
       </c>
       <c r="O5" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1814,10 +1814,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>18.75</v>
+        <v>16.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>23.05</v>
+        <v>20.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26.35</v>
+        <v>23.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>30.35</v>
+        <v>27.8</v>
       </c>
       <c r="O9" t="n">
-        <v>3.05</v>
+        <v>0.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>31.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>36.23</v>
+        <v>32.3</v>
       </c>
       <c r="O10" t="n">
-        <v>4.43</v>
+        <v>0.5</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>41.73</v>
+        <v>37.8</v>
       </c>
       <c r="O11" t="n">
-        <v>4.43</v>
+        <v>0.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         <v>43.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -2192,10 +2192,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>47.53</v>
+        <v>45.03</v>
       </c>
       <c r="O12" t="n">
-        <v>4.43</v>
+        <v>1.93</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2255,13 +2255,13 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>53.72</v>
+        <v>49.03</v>
       </c>
       <c r="O13" t="n">
-        <v>6.62</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>56.82</v>
+        <v>52.13</v>
       </c>
       <c r="O14" t="n">
-        <v>6.62</v>
+        <v>1.93</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -2381,13 +2381,13 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>59.72</v>
+        <v>55.03</v>
       </c>
       <c r="O15" t="n">
-        <v>6.62</v>
+        <v>1.93</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -2444,13 +2444,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>65.42</v>
+        <v>60.73</v>
       </c>
       <c r="O16" t="n">
-        <v>6.62</v>
+        <v>1.93</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2507,13 +2507,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>73.52</v>
+        <v>67.19</v>
       </c>
       <c r="O17" t="n">
-        <v>9.42</v>
+        <v>3.09</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -2570,13 +2570,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>77.92</v>
+        <v>71.59</v>
       </c>
       <c r="O18" t="n">
-        <v>9.42</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>75.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>85.86</v>
+        <v>78.59</v>
       </c>
       <c r="O19" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>92.86</v>
+        <v>85.59</v>
       </c>
       <c r="O20" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -2759,13 +2759,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>98.86</v>
+        <v>91.59</v>
       </c>
       <c r="O21" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -2822,13 +2822,13 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>106.16</v>
+        <v>98.89</v>
       </c>
       <c r="O22" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -2885,13 +2885,13 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>112.46</v>
+        <v>105.19</v>
       </c>
       <c r="O23" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -2948,13 +2948,13 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>118.16</v>
+        <v>110.89</v>
       </c>
       <c r="O24" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -3011,13 +3011,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>122.86</v>
+        <v>115.59</v>
       </c>
       <c r="O25" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -3074,13 +3074,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>129.86</v>
+        <v>122.59</v>
       </c>
       <c r="O26" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -3137,13 +3137,13 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>139.36</v>
+        <v>132.09</v>
       </c>
       <c r="O27" t="n">
-        <v>10.36</v>
+        <v>3.09</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
         <v>3.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3389,13 +3389,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>19.24</v>
+        <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>7.74</v>
+        <v>0.5</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -3452,13 +3452,13 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>23.44</v>
+        <v>16.2</v>
       </c>
       <c r="O32" t="n">
-        <v>7.74</v>
+        <v>0.5</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3515,13 +3515,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>30.07</v>
+        <v>20.5</v>
       </c>
       <c r="O33" t="n">
-        <v>10.07</v>
+        <v>0.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>23.3</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3578,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>33.37</v>
+        <v>25.75</v>
       </c>
       <c r="O34" t="n">
-        <v>10.07</v>
+        <v>2.45</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3641,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>41.36</v>
+        <v>29.75</v>
       </c>
       <c r="O35" t="n">
-        <v>14.06</v>
+        <v>2.45</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -3704,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>45.86</v>
+        <v>34.25</v>
       </c>
       <c r="O36" t="n">
-        <v>14.06</v>
+        <v>2.45</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         <v>37.3</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>51.36</v>
+        <v>40.92</v>
       </c>
       <c r="O37" t="n">
-        <v>14.06</v>
+        <v>3.62</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -3830,13 +3830,13 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>57.16</v>
+        <v>46.72</v>
       </c>
       <c r="O38" t="n">
-        <v>14.06</v>
+        <v>3.62</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>47.1</v>
       </c>
       <c r="J39" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3893,13 +3893,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>63.73</v>
+        <v>50.72</v>
       </c>
       <c r="O39" t="n">
-        <v>16.63</v>
+        <v>3.62</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -3956,13 +3956,13 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>66.83</v>
+        <v>53.82</v>
       </c>
       <c r="O40" t="n">
-        <v>16.63</v>
+        <v>3.62</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -4019,13 +4019,13 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>69.73</v>
+        <v>56.72</v>
       </c>
       <c r="O41" t="n">
-        <v>16.63</v>
+        <v>3.62</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -4082,13 +4082,13 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>75.43000000000001</v>
+        <v>62.42</v>
       </c>
       <c r="O42" t="n">
-        <v>16.63</v>
+        <v>3.62</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -4145,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>80.73</v>
+        <v>71.98</v>
       </c>
       <c r="O43" t="n">
-        <v>16.63</v>
+        <v>7.88</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -4208,10 +4208,10 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>85.13</v>
+        <v>76.38</v>
       </c>
       <c r="O44" t="n">
-        <v>16.63</v>
+        <v>7.88</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -4259,7 +4259,7 @@
         <v>75.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4271,10 +4271,10 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>92.13</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>16.63</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -4334,10 +4334,10 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>99.13</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>16.63</v>
+        <v>14.15</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>105.13</v>
+        <v>102.65</v>
       </c>
       <c r="O47" t="n">
-        <v>16.63</v>
+        <v>14.15</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -4448,10 +4448,10 @@
         <v>95.8</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -4460,10 +4460,10 @@
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>112.43</v>
+        <v>116.89</v>
       </c>
       <c r="O48" t="n">
-        <v>16.63</v>
+        <v>21.09</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -4511,10 +4511,10 @@
         <v>102.1</v>
       </c>
       <c r="J49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.09</v>
+        <v>3.49</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4523,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>124.72</v>
+        <v>126.68</v>
       </c>
       <c r="O49" t="n">
-        <v>22.62</v>
+        <v>24.58</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -4574,7 +4574,7 @@
         <v>107.8</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>130.42</v>
+        <v>135.3</v>
       </c>
       <c r="O50" t="n">
-        <v>22.62</v>
+        <v>27.5</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -4637,10 +4637,10 @@
         <v>112.5</v>
       </c>
       <c r="J51" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4649,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>136.21</v>
+        <v>142.87</v>
       </c>
       <c r="O51" t="n">
-        <v>23.71</v>
+        <v>30.37</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -4712,10 +4712,10 @@
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>143.21</v>
+        <v>149.87</v>
       </c>
       <c r="O52" t="n">
-        <v>23.71</v>
+        <v>30.37</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4775,10 +4775,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>152.71</v>
+        <v>159.37</v>
       </c>
       <c r="O53" t="n">
-        <v>23.71</v>
+        <v>30.37</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -5204,7 +5204,7 @@
         <v>23.3</v>
       </c>
       <c r="J60" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>26.18</v>
+        <v>23.8</v>
       </c>
       <c r="O60" t="n">
-        <v>2.88</v>
+        <v>0.5</v>
       </c>
       <c r="P60" t="n">
         <v>0</v>
@@ -5279,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>30.18</v>
+        <v>27.8</v>
       </c>
       <c r="O61" t="n">
-        <v>2.88</v>
+        <v>0.5</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>34.68</v>
+        <v>32.3</v>
       </c>
       <c r="O62" t="n">
-        <v>2.88</v>
+        <v>0.5</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5405,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>40.18</v>
+        <v>37.8</v>
       </c>
       <c r="O63" t="n">
-        <v>2.88</v>
+        <v>0.5</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
         <v>43.1</v>
       </c>
       <c r="J64" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5468,13 +5468,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>48.59</v>
+        <v>43.6</v>
       </c>
       <c r="O64" t="n">
-        <v>5.49</v>
+        <v>0.5</v>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -5531,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>52.59</v>
+        <v>47.6</v>
       </c>
       <c r="O65" t="n">
-        <v>5.49</v>
+        <v>0.5</v>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -5594,13 +5594,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>55.69</v>
+        <v>50.7</v>
       </c>
       <c r="O66" t="n">
-        <v>5.49</v>
+        <v>0.5</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -5657,13 +5657,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>58.59</v>
+        <v>53.6</v>
       </c>
       <c r="O67" t="n">
-        <v>5.49</v>
+        <v>0.5</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>58.8</v>
       </c>
       <c r="J68" t="n">
-        <v>1.27</v>
+        <v>2.28</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5720,13 +5720,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>65.56</v>
+        <v>61.58</v>
       </c>
       <c r="O68" t="n">
-        <v>6.76</v>
+        <v>2.78</v>
       </c>
       <c r="P68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -5783,13 +5783,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>70.86</v>
+        <v>66.88</v>
       </c>
       <c r="O69" t="n">
-        <v>6.76</v>
+        <v>2.78</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>75.26000000000001</v>
+        <v>74.28</v>
       </c>
       <c r="O70" t="n">
-        <v>6.76</v>
+        <v>5.78</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -5909,10 +5909,10 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>82.26000000000001</v>
+        <v>81.28</v>
       </c>
       <c r="O71" t="n">
-        <v>6.76</v>
+        <v>5.78</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -5972,10 +5972,10 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>89.26000000000001</v>
+        <v>88.28</v>
       </c>
       <c r="O72" t="n">
-        <v>6.76</v>
+        <v>5.78</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
@@ -6023,7 +6023,7 @@
         <v>88.5</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6035,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>95.26000000000001</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="O73" t="n">
-        <v>6.76</v>
+        <v>7.24</v>
       </c>
       <c r="P73" t="n">
         <v>1</v>
@@ -6092,16 +6092,16 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>10.99</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>113.55</v>
+        <v>111.49</v>
       </c>
       <c r="O74" t="n">
-        <v>17.75</v>
+        <v>15.69</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -6155,16 +6155,16 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>9.109999999999999</v>
+        <v>10.91</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>128.96</v>
+        <v>128.7</v>
       </c>
       <c r="O75" t="n">
-        <v>26.86</v>
+        <v>26.6</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -6212,22 +6212,22 @@
         <v>107.8</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>11.15</v>
+        <v>14.33</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>145.81</v>
+        <v>150.57</v>
       </c>
       <c r="O76" t="n">
-        <v>38.01</v>
+        <v>42.77</v>
       </c>
       <c r="P76" t="n">
         <v>1</v>
@@ -6281,16 +6281,16 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>13.88</v>
+        <v>14</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>164.39</v>
+        <v>169.27</v>
       </c>
       <c r="O77" t="n">
-        <v>51.89</v>
+        <v>56.77</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -6344,16 +6344,16 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>13.44</v>
+        <v>10.66</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>184.83</v>
+        <v>186.93</v>
       </c>
       <c r="O78" t="n">
-        <v>65.33</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -6401,22 +6401,22 @@
         <v>129</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>9.67</v>
+        <v>13.97</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>204</v>
+        <v>212.1</v>
       </c>
       <c r="O79" t="n">
-        <v>75</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
@@ -6590,7 +6590,7 @@
         <v>6.5</v>
       </c>
       <c r="J82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -6602,10 +6602,10 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>8.67</v>
+        <v>7</v>
       </c>
       <c r="O82" t="n">
-        <v>2.17</v>
+        <v>0.5</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6656,7 +6656,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -6665,10 +6665,10 @@
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>16.2</v>
+        <v>12</v>
       </c>
       <c r="O83" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -6728,10 +6728,10 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>20.4</v>
+        <v>16.2</v>
       </c>
       <c r="O84" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -6791,13 +6791,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>26.13</v>
+        <v>21.94</v>
       </c>
       <c r="O85" t="n">
-        <v>6.13</v>
+        <v>1.94</v>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -6854,13 +6854,13 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>29.43</v>
+        <v>25.24</v>
       </c>
       <c r="O86" t="n">
-        <v>6.13</v>
+        <v>1.94</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>27.3</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -6917,13 +6917,13 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>33.43</v>
+        <v>30.91</v>
       </c>
       <c r="O87" t="n">
-        <v>6.13</v>
+        <v>3.61</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>31.8</v>
       </c>
       <c r="J88" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -6980,13 +6980,13 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>40.6</v>
+        <v>35.41</v>
       </c>
       <c r="O88" t="n">
-        <v>8.800000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -7043,13 +7043,13 @@
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>46.1</v>
+        <v>40.91</v>
       </c>
       <c r="O89" t="n">
-        <v>8.800000000000001</v>
+        <v>3.61</v>
       </c>
       <c r="P89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>43.1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -7106,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>51.9</v>
+        <v>48.64</v>
       </c>
       <c r="O90" t="n">
-        <v>8.800000000000001</v>
+        <v>5.54</v>
       </c>
       <c r="P90" t="n">
         <v>1</v>
@@ -7157,10 +7157,10 @@
         <v>47.1</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="K91" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>60.98</v>
+        <v>54.88</v>
       </c>
       <c r="O91" t="n">
-        <v>13.88</v>
+        <v>7.78</v>
       </c>
       <c r="P91" t="n">
         <v>1</v>
@@ -7220,7 +7220,7 @@
         <v>50.2</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7232,10 +7232,10 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>64.08</v>
+        <v>59.77</v>
       </c>
       <c r="O92" t="n">
-        <v>13.88</v>
+        <v>9.57</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -7295,10 +7295,10 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>66.98</v>
+        <v>62.67</v>
       </c>
       <c r="O93" t="n">
-        <v>13.88</v>
+        <v>9.57</v>
       </c>
       <c r="P93" t="n">
         <v>1</v>
@@ -7346,10 +7346,10 @@
         <v>58.8</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -7358,10 +7358,10 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>72.68000000000001</v>
+        <v>74.28</v>
       </c>
       <c r="O94" t="n">
-        <v>13.88</v>
+        <v>15.48</v>
       </c>
       <c r="P94" t="n">
         <v>1</v>
@@ -7409,10 +7409,10 @@
         <v>64.09999999999999</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="K95" t="n">
-        <v>5.12</v>
+        <v>3.14</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -7421,10 +7421,10 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>83.09999999999999</v>
+        <v>84.48</v>
       </c>
       <c r="O95" t="n">
-        <v>19</v>
+        <v>20.38</v>
       </c>
       <c r="P95" t="n">
         <v>1</v>
@@ -7475,19 +7475,19 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="L96" t="n">
-        <v>14.31</v>
+        <v>16.66</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>101.81</v>
+        <v>110.17</v>
       </c>
       <c r="O96" t="n">
-        <v>33.31</v>
+        <v>41.67</v>
       </c>
       <c r="P96" t="n">
         <v>1</v>
@@ -7541,16 +7541,16 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>16.4</v>
+        <v>10.66</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>125.21</v>
+        <v>127.83</v>
       </c>
       <c r="O97" t="n">
-        <v>49.71</v>
+        <v>52.33</v>
       </c>
       <c r="P97" t="n">
         <v>1</v>
@@ -7598,22 +7598,22 @@
         <v>82.5</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>13.91</v>
+        <v>12.8</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>146.12</v>
+        <v>149.71</v>
       </c>
       <c r="O98" t="n">
-        <v>63.62</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="P98" t="n">
         <v>1</v>
@@ -7667,16 +7667,16 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>13.11</v>
+        <v>16.25</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>165.23</v>
+        <v>171.96</v>
       </c>
       <c r="O99" t="n">
-        <v>76.73</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -7730,16 +7730,16 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>16.39</v>
+        <v>17.6</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>188.92</v>
+        <v>196.86</v>
       </c>
       <c r="O100" t="n">
-        <v>93.12</v>
+        <v>101.06</v>
       </c>
       <c r="P100" t="n">
         <v>1</v>
@@ -7787,22 +7787,22 @@
         <v>102.1</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="L101" t="n">
-        <v>17.36</v>
+        <v>15.36</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>212.58</v>
+        <v>222</v>
       </c>
       <c r="O101" t="n">
-        <v>110.48</v>
+        <v>119.9</v>
       </c>
       <c r="P101" t="n">
         <v>1</v>
@@ -7856,16 +7856,16 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>14.27</v>
+        <v>11.74</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>232.55</v>
+        <v>239.44</v>
       </c>
       <c r="O102" t="n">
-        <v>124.75</v>
+        <v>131.64</v>
       </c>
       <c r="P102" t="n">
         <v>1</v>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="L103" t="n">
-        <v>14.74</v>
+        <v>11.34</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>251.99</v>
+        <v>255.48</v>
       </c>
       <c r="O103" t="n">
-        <v>139.49</v>
+        <v>142.98</v>
       </c>
       <c r="P103" t="n">
         <v>1</v>
@@ -7982,16 +7982,16 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>10.67</v>
+        <v>15.98</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>269.66</v>
+        <v>278.46</v>
       </c>
       <c r="O104" t="n">
-        <v>150.16</v>
+        <v>158.96</v>
       </c>
       <c r="P104" t="n">
         <v>1</v>
@@ -8039,22 +8039,22 @@
         <v>129</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>16.93</v>
+        <v>10.86</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>296.09</v>
+        <v>301.46</v>
       </c>
       <c r="O105" t="n">
-        <v>167.09</v>
+        <v>172.46</v>
       </c>
       <c r="P105" t="n">
         <v>1</v>
@@ -8102,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         <v>20</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -8429,10 +8429,10 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>20.5</v>
+        <v>22.88</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5</v>
+        <v>2.88</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
@@ -8492,10 +8492,10 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>23.8</v>
+        <v>26.18</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5</v>
+        <v>2.88</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -8543,7 +8543,7 @@
         <v>27.3</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -8555,13 +8555,13 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>27.8</v>
+        <v>32.72</v>
       </c>
       <c r="O113" t="n">
-        <v>0.5</v>
+        <v>5.42</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -8618,10 +8618,10 @@
         <v>35</v>
       </c>
       <c r="N114" t="n">
-        <v>67.3</v>
+        <v>72.22</v>
       </c>
       <c r="O114" t="n">
-        <v>35.5</v>
+        <v>40.42</v>
       </c>
       <c r="P114" t="n">
         <v>1</v>
@@ -8669,7 +8669,7 @@
         <v>37.3</v>
       </c>
       <c r="J115" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -8681,10 +8681,10 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>75.7</v>
+        <v>77.72</v>
       </c>
       <c r="O115" t="n">
-        <v>38.4</v>
+        <v>40.42</v>
       </c>
       <c r="P115" t="n">
         <v>1</v>
@@ -8732,7 +8732,7 @@
         <v>43.1</v>
       </c>
       <c r="J116" t="n">
-        <v>1.14</v>
+        <v>2.97</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -8744,10 +8744,10 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>82.64</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="O116" t="n">
-        <v>39.54</v>
+        <v>43.39</v>
       </c>
       <c r="P116" t="n">
         <v>1</v>
@@ -8798,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -8807,10 +8807,10 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>88.75</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="O117" t="n">
-        <v>41.65</v>
+        <v>43.39</v>
       </c>
       <c r="P117" t="n">
         <v>1</v>
@@ -8858,7 +8858,7 @@
         <v>50.2</v>
       </c>
       <c r="J118" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -8870,10 +8870,10 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>94.53</v>
+        <v>93.59</v>
       </c>
       <c r="O118" t="n">
-        <v>44.33</v>
+        <v>43.39</v>
       </c>
       <c r="P118" t="n">
         <v>1</v>
@@ -8933,10 +8933,10 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>97.43000000000001</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="O119" t="n">
-        <v>44.33</v>
+        <v>43.39</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         <v>58.8</v>
       </c>
       <c r="J120" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -8996,10 +8996,10 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>105.08</v>
+        <v>102.19</v>
       </c>
       <c r="O120" t="n">
-        <v>46.28</v>
+        <v>43.39</v>
       </c>
       <c r="P120" t="n">
         <v>1</v>
@@ -9047,7 +9047,7 @@
         <v>64.09999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -9059,10 +9059,10 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>113.28</v>
+        <v>107.49</v>
       </c>
       <c r="O121" t="n">
-        <v>49.18</v>
+        <v>43.39</v>
       </c>
       <c r="P121" t="n">
         <v>1</v>
@@ -9113,7 +9113,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -9122,10 +9122,10 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>117.68</v>
+        <v>117.25</v>
       </c>
       <c r="O122" t="n">
-        <v>49.18</v>
+        <v>48.75</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
@@ -9185,10 +9185,10 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>124.68</v>
+        <v>124.25</v>
       </c>
       <c r="O123" t="n">
-        <v>49.18</v>
+        <v>48.75</v>
       </c>
       <c r="P123" t="n">
         <v>1</v>
@@ -9248,10 +9248,10 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>131.68</v>
+        <v>131.25</v>
       </c>
       <c r="O124" t="n">
-        <v>49.18</v>
+        <v>48.75</v>
       </c>
       <c r="P124" t="n">
         <v>1</v>
@@ -9311,10 +9311,10 @@
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>137.68</v>
+        <v>137.25</v>
       </c>
       <c r="O125" t="n">
-        <v>49.18</v>
+        <v>48.75</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
@@ -9374,10 +9374,10 @@
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>144.98</v>
+        <v>144.55</v>
       </c>
       <c r="O126" t="n">
-        <v>49.18</v>
+        <v>48.75</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
@@ -9425,7 +9425,7 @@
         <v>102.1</v>
       </c>
       <c r="J127" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -9437,10 +9437,10 @@
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>152.9</v>
+        <v>150.85</v>
       </c>
       <c r="O127" t="n">
-        <v>50.8</v>
+        <v>48.75</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
@@ -9500,10 +9500,10 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>158.6</v>
+        <v>156.55</v>
       </c>
       <c r="O128" t="n">
-        <v>50.8</v>
+        <v>48.75</v>
       </c>
       <c r="P128" t="n">
         <v>1</v>
@@ -9563,10 +9563,10 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>163.3</v>
+        <v>161.25</v>
       </c>
       <c r="O129" t="n">
-        <v>50.8</v>
+        <v>48.75</v>
       </c>
       <c r="P129" t="n">
         <v>1</v>
@@ -9626,10 +9626,10 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>170.3</v>
+        <v>168.25</v>
       </c>
       <c r="O130" t="n">
-        <v>50.8</v>
+        <v>48.75</v>
       </c>
       <c r="P130" t="n">
         <v>1</v>
@@ -9689,10 +9689,10 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>179.8</v>
+        <v>177.75</v>
       </c>
       <c r="O131" t="n">
-        <v>50.8</v>
+        <v>48.75</v>
       </c>
       <c r="P131" t="n">
         <v>1</v>
@@ -9904,7 +9904,7 @@
         <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.18</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -9916,10 +9916,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>6.18</v>
+        <v>6.76</v>
       </c>
       <c r="O3" t="n">
-        <v>2.68</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -9967,7 +9967,7 @@
         <v>6.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -9979,13 +9979,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9.18</v>
+        <v>11.69</v>
       </c>
       <c r="O4" t="n">
-        <v>2.68</v>
+        <v>5.19</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -10030,10 +10030,10 @@
         <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -10042,10 +10042,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>20.96</v>
+        <v>16.69</v>
       </c>
       <c r="O5" t="n">
-        <v>9.460000000000001</v>
+        <v>5.19</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>25.16</v>
+        <v>20.89</v>
       </c>
       <c r="O6" t="n">
-        <v>9.460000000000001</v>
+        <v>5.19</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -10156,7 +10156,7 @@
         <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -10168,10 +10168,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>29.46</v>
+        <v>27.89</v>
       </c>
       <c r="O7" t="n">
-        <v>9.460000000000001</v>
+        <v>7.89</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>23.3</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -10231,10 +10231,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>32.76</v>
+        <v>32.61</v>
       </c>
       <c r="O8" t="n">
-        <v>9.460000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -10282,7 +10282,7 @@
         <v>27.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -10294,10 +10294,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>38.83</v>
+        <v>36.61</v>
       </c>
       <c r="O9" t="n">
-        <v>11.53</v>
+        <v>9.31</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -10345,7 +10345,7 @@
         <v>31.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>45.63</v>
+        <v>41.11</v>
       </c>
       <c r="O10" t="n">
-        <v>13.83</v>
+        <v>9.31</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -10408,7 +10408,7 @@
         <v>37.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -10420,10 +10420,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>52.97</v>
+        <v>46.61</v>
       </c>
       <c r="O11" t="n">
-        <v>15.67</v>
+        <v>9.31</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -10483,10 +10483,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>58.77</v>
+        <v>52.41</v>
       </c>
       <c r="O12" t="n">
-        <v>15.67</v>
+        <v>9.31</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -10537,7 +10537,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -10546,10 +10546,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>67.89</v>
+        <v>56.41</v>
       </c>
       <c r="O13" t="n">
-        <v>20.79</v>
+        <v>9.31</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -10597,7 +10597,7 @@
         <v>50.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -10609,10 +10609,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>70.98999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="O14" t="n">
-        <v>20.79</v>
+        <v>12.21</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -10660,7 +10660,7 @@
         <v>53.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.35</v>
+        <v>2.44</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -10672,10 +10672,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>75.23999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="O15" t="n">
-        <v>22.14</v>
+        <v>14.65</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -10735,10 +10735,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>80.94</v>
+        <v>73.45</v>
       </c>
       <c r="O16" t="n">
-        <v>22.14</v>
+        <v>14.65</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -10798,10 +10798,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>86.23999999999999</v>
+        <v>78.75</v>
       </c>
       <c r="O17" t="n">
-        <v>22.14</v>
+        <v>14.65</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -10861,10 +10861,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>90.64</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>22.14</v>
+        <v>14.65</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -10912,7 +10912,7 @@
         <v>75.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -10924,10 +10924,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>97.64</v>
+        <v>91.59</v>
       </c>
       <c r="O19" t="n">
-        <v>22.14</v>
+        <v>16.09</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -10978,7 +10978,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -10987,10 +10987,10 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>104.64</v>
+        <v>102.63</v>
       </c>
       <c r="O20" t="n">
-        <v>22.14</v>
+        <v>20.13</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -11050,10 +11050,10 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>110.64</v>
+        <v>108.63</v>
       </c>
       <c r="O21" t="n">
-        <v>22.14</v>
+        <v>20.13</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -11113,10 +11113,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>117.94</v>
+        <v>115.93</v>
       </c>
       <c r="O22" t="n">
-        <v>22.14</v>
+        <v>20.13</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -11164,10 +11164,10 @@
         <v>102.1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.58</v>
+        <v>4.46</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>130.69</v>
+        <v>126.69</v>
       </c>
       <c r="O23" t="n">
-        <v>28.59</v>
+        <v>24.59</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -11239,10 +11239,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>136.39</v>
+        <v>132.39</v>
       </c>
       <c r="O24" t="n">
-        <v>28.59</v>
+        <v>24.59</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -11293,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -11302,10 +11302,10 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>141.09</v>
+        <v>139.76</v>
       </c>
       <c r="O25" t="n">
-        <v>28.59</v>
+        <v>27.26</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -11353,7 +11353,7 @@
         <v>119.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -11365,10 +11365,10 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>148.09</v>
+        <v>148.83</v>
       </c>
       <c r="O26" t="n">
-        <v>28.59</v>
+        <v>29.33</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -11419,7 +11419,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -11428,10 +11428,10 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>157.59</v>
+        <v>161.09</v>
       </c>
       <c r="O27" t="n">
-        <v>28.59</v>
+        <v>32.09</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -11671,7 +11671,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -11680,10 +11680,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>14.98</v>
+        <v>12</v>
       </c>
       <c r="O31" t="n">
-        <v>3.48</v>
+        <v>0.5</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -11743,10 +11743,10 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>19.18</v>
+        <v>16.2</v>
       </c>
       <c r="O32" t="n">
-        <v>3.48</v>
+        <v>0.5</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -11806,10 +11806,10 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>23.48</v>
+        <v>21.89</v>
       </c>
       <c r="O33" t="n">
-        <v>3.48</v>
+        <v>1.89</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -11857,7 +11857,7 @@
         <v>23.3</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -11869,10 +11869,10 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>26.78</v>
+        <v>26.55</v>
       </c>
       <c r="O34" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -11920,10 +11920,10 @@
         <v>27.3</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="K35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -11932,10 +11932,10 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>33.62</v>
+        <v>32.62</v>
       </c>
       <c r="O35" t="n">
-        <v>6.32</v>
+        <v>5.32</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -11995,10 +11995,10 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>38.12</v>
+        <v>37.12</v>
       </c>
       <c r="O36" t="n">
-        <v>6.32</v>
+        <v>5.32</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -12052,16 +12052,16 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>7.44</v>
+        <v>9.32</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>51.06</v>
+        <v>51.94</v>
       </c>
       <c r="O37" t="n">
-        <v>13.76</v>
+        <v>14.64</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -12115,16 +12115,16 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>10.27</v>
+        <v>6.76</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>67.13</v>
+        <v>64.5</v>
       </c>
       <c r="O38" t="n">
-        <v>24.03</v>
+        <v>21.4</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -12175,19 +12175,19 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>8.43</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>82.59</v>
+        <v>77.45</v>
       </c>
       <c r="O39" t="n">
-        <v>35.49</v>
+        <v>30.35</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -12235,22 +12235,22 @@
         <v>50.2</v>
       </c>
       <c r="J40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>8.210000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>96.23</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>46.03</v>
+        <v>39.79</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -12304,16 +12304,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>8.06</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>107.19</v>
+        <v>101.53</v>
       </c>
       <c r="O41" t="n">
-        <v>54.09</v>
+        <v>48.43</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -12361,22 +12361,22 @@
         <v>58.8</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>9.300000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>122.19</v>
+        <v>117.2</v>
       </c>
       <c r="O42" t="n">
-        <v>63.39</v>
+        <v>58.4</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -12430,16 +12430,16 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>7.84</v>
+        <v>6.44</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>135.33</v>
+        <v>128.94</v>
       </c>
       <c r="O43" t="n">
-        <v>71.23</v>
+        <v>64.84</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -12487,22 +12487,22 @@
         <v>68.5</v>
       </c>
       <c r="J44" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="L44" t="n">
-        <v>7.89</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>150.06</v>
+        <v>145.24</v>
       </c>
       <c r="O44" t="n">
-        <v>81.56</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -12556,16 +12556,16 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>11.71</v>
+        <v>11.96</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>168.77</v>
+        <v>164.2</v>
       </c>
       <c r="O45" t="n">
-        <v>93.27</v>
+        <v>88.7</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -12613,22 +12613,22 @@
         <v>82.5</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>7.15</v>
+        <v>10.74</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>182.92</v>
+        <v>184.47</v>
       </c>
       <c r="O46" t="n">
-        <v>100.42</v>
+        <v>101.97</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -12676,22 +12676,22 @@
         <v>88.5</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="K47" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>10.56</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>203.54</v>
+        <v>201.22</v>
       </c>
       <c r="O47" t="n">
-        <v>115.04</v>
+        <v>112.72</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -12745,16 +12745,16 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>222.72</v>
+        <v>220.46</v>
       </c>
       <c r="O48" t="n">
-        <v>126.92</v>
+        <v>124.66</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -12805,19 +12805,19 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>7.81</v>
+        <v>9.66</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>240.09</v>
+        <v>236.42</v>
       </c>
       <c r="O49" t="n">
-        <v>137.99</v>
+        <v>134.32</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -12871,16 +12871,16 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>6.76</v>
+        <v>11.69</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>252.55</v>
+        <v>253.81</v>
       </c>
       <c r="O50" t="n">
-        <v>144.75</v>
+        <v>146.01</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -12928,22 +12928,22 @@
         <v>112.5</v>
       </c>
       <c r="J51" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>7.75</v>
+        <v>6.94</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>266.11</v>
+        <v>266.87</v>
       </c>
       <c r="O51" t="n">
-        <v>153.61</v>
+        <v>154.37</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -12991,22 +12991,22 @@
         <v>119.5</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>9.83</v>
+        <v>6.02</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>282.94</v>
+        <v>281.04</v>
       </c>
       <c r="O52" t="n">
-        <v>163.44</v>
+        <v>161.54</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -13060,16 +13060,16 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>6.62</v>
+        <v>7.75</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>299.06</v>
+        <v>298.29</v>
       </c>
       <c r="O53" t="n">
-        <v>170.06</v>
+        <v>169.29</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1.57</v>
+        <v>2.41</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -13309,7 +13309,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -13318,13 +13318,13 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>17.02</v>
+        <v>12</v>
       </c>
       <c r="O57" t="n">
-        <v>5.52</v>
+        <v>0.5</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>15.7</v>
       </c>
       <c r="J58" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -13381,13 +13381,13 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>22.35</v>
+        <v>16.2</v>
       </c>
       <c r="O58" t="n">
-        <v>6.65</v>
+        <v>0.5</v>
       </c>
       <c r="P58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -13444,13 +13444,13 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>26.65</v>
+        <v>20.5</v>
       </c>
       <c r="O59" t="n">
-        <v>6.65</v>
+        <v>0.5</v>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -13507,13 +13507,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>29.95</v>
+        <v>23.8</v>
       </c>
       <c r="O60" t="n">
-        <v>6.65</v>
+        <v>0.5</v>
       </c>
       <c r="P60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -13570,13 +13570,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>38.79</v>
+        <v>27.8</v>
       </c>
       <c r="O61" t="n">
-        <v>11.49</v>
+        <v>0.5</v>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -13633,13 +13633,13 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>43.29</v>
+        <v>32.3</v>
       </c>
       <c r="O62" t="n">
-        <v>11.49</v>
+        <v>0.5</v>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>37.3</v>
       </c>
       <c r="J63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -13696,13 +13696,13 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>50.29</v>
+        <v>37.8</v>
       </c>
       <c r="O63" t="n">
-        <v>12.99</v>
+        <v>0.5</v>
       </c>
       <c r="P63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -13759,13 +13759,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>56.09</v>
+        <v>43.6</v>
       </c>
       <c r="O64" t="n">
-        <v>12.99</v>
+        <v>0.5</v>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -13822,13 +13822,13 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>60.09</v>
+        <v>47.6</v>
       </c>
       <c r="O65" t="n">
-        <v>12.99</v>
+        <v>0.5</v>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -13885,13 +13885,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>63.19</v>
+        <v>50.7</v>
       </c>
       <c r="O66" t="n">
-        <v>12.99</v>
+        <v>0.5</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -13948,13 +13948,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>66.09</v>
+        <v>53.6</v>
       </c>
       <c r="O67" t="n">
-        <v>12.99</v>
+        <v>0.5</v>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -13999,10 +13999,10 @@
         <v>58.8</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -14011,10 +14011,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>71.79000000000001</v>
+        <v>65.25</v>
       </c>
       <c r="O68" t="n">
-        <v>12.99</v>
+        <v>6.45</v>
       </c>
       <c r="P68" t="n">
         <v>1</v>
@@ -14065,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>4.06</v>
+        <v>2.44</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -14074,10 +14074,10 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>81.15000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="O69" t="n">
-        <v>17.05</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
@@ -14137,10 +14137,10 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>85.55</v>
+        <v>77.39</v>
       </c>
       <c r="O70" t="n">
-        <v>17.05</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
@@ -14200,10 +14200,10 @@
         <v>45</v>
       </c>
       <c r="N71" t="n">
-        <v>137.55</v>
+        <v>129.39</v>
       </c>
       <c r="O71" t="n">
-        <v>62.05</v>
+        <v>53.89</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
@@ -14251,7 +14251,7 @@
         <v>82.5</v>
       </c>
       <c r="J72" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -14263,10 +14263,10 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>147.47</v>
+        <v>136.39</v>
       </c>
       <c r="O72" t="n">
-        <v>64.97</v>
+        <v>53.89</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
@@ -14314,7 +14314,7 @@
         <v>88.5</v>
       </c>
       <c r="J73" t="n">
-        <v>2.53</v>
+        <v>1.08</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -14326,10 +14326,10 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>156</v>
+        <v>143.47</v>
       </c>
       <c r="O73" t="n">
-        <v>67.5</v>
+        <v>54.97</v>
       </c>
       <c r="P73" t="n">
         <v>1</v>
@@ -14380,7 +14380,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>163.3</v>
+        <v>153.65</v>
       </c>
       <c r="O74" t="n">
-        <v>67.5</v>
+        <v>57.85</v>
       </c>
       <c r="P74" t="n">
         <v>1</v>
@@ -14440,7 +14440,7 @@
         <v>102.1</v>
       </c>
       <c r="J75" t="n">
-        <v>1.48</v>
+        <v>2.92</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -14452,10 +14452,10 @@
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>171.08</v>
+        <v>162.87</v>
       </c>
       <c r="O75" t="n">
-        <v>68.98</v>
+        <v>60.77</v>
       </c>
       <c r="P75" t="n">
         <v>1</v>
@@ -14503,7 +14503,7 @@
         <v>107.8</v>
       </c>
       <c r="J76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -14515,10 +14515,10 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>178.6</v>
+        <v>168.57</v>
       </c>
       <c r="O76" t="n">
-        <v>70.8</v>
+        <v>60.77</v>
       </c>
       <c r="P76" t="n">
         <v>1</v>
@@ -14578,10 +14578,10 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>183.3</v>
+        <v>173.27</v>
       </c>
       <c r="O77" t="n">
-        <v>70.8</v>
+        <v>60.77</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -14641,10 +14641,10 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>190.3</v>
+        <v>180.27</v>
       </c>
       <c r="O78" t="n">
-        <v>70.8</v>
+        <v>60.77</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -14692,10 +14692,10 @@
         <v>129</v>
       </c>
       <c r="J79" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -14704,10 +14704,10 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>201.38</v>
+        <v>194.42</v>
       </c>
       <c r="O79" t="n">
-        <v>72.38</v>
+        <v>65.42</v>
       </c>
       <c r="P79" t="n">
         <v>1</v>
@@ -16172,7 +16172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16188,35 +16188,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>location_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>kilometer_marker</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>between_station_from</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>between_station_to</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>station_pair</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>open_timestamp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>close_timestamp</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>open_duration_seconds</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>delay_impact_minutes</t>
         </is>
@@ -16228,34 +16238,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>19</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>52.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>2026-09-15 00:05:16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>2026-09-15 00:11:31</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>375</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>6.25</v>
       </c>
     </row>
@@ -16265,35 +16283,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>19</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D3" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E3" t="n">
         <v>20</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-09-15 00:33:13</t>
-        </is>
+      <c r="F3" t="n">
+        <v>21</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:41:10</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>477</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7.95</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:26:59</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:33:17</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>378</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4">
@@ -16302,35 +16328,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>15</v>
+          <t>LC-52</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Potheri (SRM University Link)</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-09-15 00:46:45</t>
-        </is>
+        <v>44.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:52:04</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>319</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.32</v>
+          <t>STA_W - STA_X</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:49:25</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-15 00:56:16</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>411</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.85</v>
       </c>
     </row>
     <row r="5">
@@ -16339,35 +16373,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>19</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-15 01:11:28</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-15 01:19:18</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>470</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.83</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:14:57</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:21:09</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>372</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.2</v>
       </c>
     </row>
     <row r="6">
@@ -16376,35 +16418,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-09-15 01:34:07</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-15 01:39:10</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>303</v>
-      </c>
-      <c r="I6" t="n">
-        <v>5.05</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:23:15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:28:12</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>297</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.95</v>
       </c>
     </row>
     <row r="7">
@@ -16413,35 +16463,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>19</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D7" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E7" t="n">
         <v>20</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-15 01:42:21</t>
-        </is>
+      <c r="F7" t="n">
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-15 01:46:26</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>245</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.08</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:50:01</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-15 01:56:31</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>390</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -16450,35 +16508,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-15 02:07:37</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>16</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-15 02:12:33</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>296</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.93</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:07:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:11:18</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>258</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="9">
@@ -16487,35 +16553,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>3</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-09-15 02:22:45</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-15 02:29:26</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>401</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.68</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:27:04</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:34:55</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>471</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.85</v>
       </c>
     </row>
     <row r="10">
@@ -16524,35 +16598,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>3</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-15 02:47:04</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-15 02:54:55</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>471</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.85</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:50:04</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-15 02:56:15</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>371</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.18</v>
       </c>
     </row>
     <row r="11">
@@ -16561,35 +16643,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>7</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-09-15 03:10:04</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-15 03:16:15</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>371</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.18</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:08:42</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:14:46</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>364</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.07</v>
       </c>
     </row>
     <row r="12">
@@ -16598,35 +16688,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-09-15 03:28:42</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-15 03:34:46</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>364</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.07</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:24:46</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:32:45</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>479</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.98</v>
       </c>
     </row>
     <row r="13">
@@ -16635,35 +16733,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>19</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-09-15 03:44:46</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-15 03:52:45</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>479</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7.98</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:47:50</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-15 03:53:51</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>361</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.02</v>
       </c>
     </row>
     <row r="14">
@@ -16672,35 +16778,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>15</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-09-15 04:15:15</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" t="n">
+        <v>26</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-15 04:22:35</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>440</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.33</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:06:06</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:10:30</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>264</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="15">
@@ -16709,35 +16823,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-09-15 04:33:12</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>26</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-15 04:37:36</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>264</v>
-      </c>
-      <c r="I15" t="n">
-        <v>4.4</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:31:27</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:37:12</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>345</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="16">
@@ -16746,35 +16868,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>15</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D16" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E16" t="n">
         <v>16</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-09-15 04:53:22</t>
-        </is>
+      <c r="F16" t="n">
+        <v>17</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-15 04:59:10</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>348</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5.8</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:41:43</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-15 04:48:30</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>407</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.78</v>
       </c>
     </row>
     <row r="17">
@@ -16783,34 +16913,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3</v>
+          <t>LC-52</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Potheri (SRM University Link)</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-09-15 05:14:55</t>
-        </is>
+        <v>44.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-15 05:22:01</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
+          <t>STA_W - STA_X</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:01:25</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:08:31</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
         <v>426</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -16820,35 +16958,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
         <v>21</v>
       </c>
-      <c r="D18" t="n">
-        <v>22</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-09-15 05:23:03</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-15 05:28:46</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>343</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5.72</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:23:15</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:28:04</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>289</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.82</v>
       </c>
     </row>
     <row r="19">
@@ -16857,35 +17003,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-09-15 05:50:51</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" t="n">
+        <v>19</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-15 05:58:31</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>460</v>
-      </c>
-      <c r="I19" t="n">
-        <v>7.67</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:54:08</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-15 05:59:56</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>348</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="20">
@@ -16894,35 +17048,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>19</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-09-15 06:07:12</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" t="n">
+        <v>17</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-15 06:12:00</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>288</v>
-      </c>
-      <c r="I20" t="n">
-        <v>4.8</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:08:29</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:13:32</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>303</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.05</v>
       </c>
     </row>
     <row r="21">
@@ -16931,35 +17093,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>7</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-15 06:34:08</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-15 06:39:56</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>348</v>
-      </c>
-      <c r="I21" t="n">
-        <v>5.8</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:34:51</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:42:31</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>460</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.67</v>
       </c>
     </row>
     <row r="22">
@@ -16968,35 +17138,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-09-15 06:48:29</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>16</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-15 06:53:32</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>303</v>
-      </c>
-      <c r="I22" t="n">
-        <v>5.05</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:41:41</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-15 06:47:59</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>378</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="23">
@@ -17005,35 +17183,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>19</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D23" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E23" t="n">
         <v>20</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-09-15 07:14:51</t>
-        </is>
+      <c r="F23" t="n">
+        <v>21</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-15 07:22:31</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>460</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7.67</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:02:59</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:10:11</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>432</v>
+      </c>
+      <c r="K23" t="n">
+        <v>7.2</v>
       </c>
     </row>
     <row r="24">
@@ -17042,35 +17228,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>19</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-09-15 07:23:03</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>26</v>
+      </c>
+      <c r="F24" t="n">
+        <v>26</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-15 07:29:49</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>406</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6.77</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:25:26</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:31:30</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>364</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.07</v>
       </c>
     </row>
     <row r="25">
@@ -17079,35 +17273,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>7</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-15 07:40:05</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>16</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-15 07:48:02</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>477</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7.95</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:46:55</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-15 07:52:37</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>342</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.7</v>
       </c>
     </row>
     <row r="26">
@@ -17116,35 +17318,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>15</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-09-15 08:05:26</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>26</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-15 08:11:30</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>364</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6.07</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:05:24</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:09:24</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>240</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -17153,35 +17363,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>3</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-09-15 08:26:55</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-15 08:32:37</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>342</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.7</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:28:59</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:36:19</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>440</v>
+      </c>
+      <c r="K27" t="n">
+        <v>7.33</v>
       </c>
     </row>
     <row r="28">
@@ -17190,35 +17408,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>15</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-09-15 08:45:24</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>26</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-15 08:49:24</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>240</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:49:27</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:56:25</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>418</v>
+      </c>
+      <c r="K28" t="n">
+        <v>6.97</v>
       </c>
     </row>
     <row r="29">
@@ -17227,35 +17453,43 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>15</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-15 09:08:59</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-15 09:16:19</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>440</v>
-      </c>
-      <c r="I29" t="n">
-        <v>7.33</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:04:12</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:09:27</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>315</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="30">
@@ -17264,35 +17498,43 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>21</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>22</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-15 09:29:27</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-15 09:36:25</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>418</v>
-      </c>
-      <c r="I30" t="n">
-        <v>6.97</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:21:37</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:28:45</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>428</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7.13</v>
       </c>
     </row>
     <row r="31">
@@ -17301,35 +17543,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-15 09:55:09</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>26</v>
+      </c>
+      <c r="F31" t="n">
+        <v>26</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-15 09:59:57</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>288</v>
-      </c>
-      <c r="I31" t="n">
-        <v>4.8</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:50:03</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-15 09:54:15</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>252</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="32">
@@ -17338,35 +17588,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>21</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-15 10:06:03</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16</v>
+      </c>
+      <c r="F32" t="n">
+        <v>17</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-15 10:12:31</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>388</v>
-      </c>
-      <c r="I32" t="n">
-        <v>6.47</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:05:03</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:11:13</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>370</v>
+      </c>
+      <c r="K32" t="n">
+        <v>6.17</v>
       </c>
     </row>
     <row r="33">
@@ -17375,35 +17633,43 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>3</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-15 10:21:47</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16</v>
+      </c>
+      <c r="F33" t="n">
+        <v>17</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-15 10:27:07</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>320</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5.33</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:25:04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:31:36</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>392</v>
+      </c>
+      <c r="K33" t="n">
+        <v>6.53</v>
       </c>
     </row>
     <row r="34">
@@ -17412,35 +17678,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>19</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D34" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E34" t="n">
         <v>20</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-15 10:41:37</t>
-        </is>
+      <c r="F34" t="n">
+        <v>21</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-15 10:47:39</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>362</v>
-      </c>
-      <c r="I34" t="n">
-        <v>6.03</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:47:25</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:55</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>270</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="35">
@@ -17449,35 +17723,43 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>3</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:05:03</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>25</v>
+      </c>
+      <c r="F35" t="n">
+        <v>26</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-15 11:11:13</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>370</v>
-      </c>
-      <c r="I35" t="n">
-        <v>6.17</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:39</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:05:59</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>260</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="36">
@@ -17486,35 +17768,43 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>3</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:25:04</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-15 11:31:36</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>392</v>
-      </c>
-      <c r="I36" t="n">
-        <v>6.53</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:30:59</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:36:05</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>306</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5.1</v>
       </c>
     </row>
     <row r="37">
@@ -17523,35 +17813,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>19</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:47:25</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" t="n">
+        <v>26</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-15 11:51:55</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>270</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4.5</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:50:15</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:55:22</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>307</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.12</v>
       </c>
     </row>
     <row r="38">
@@ -17560,35 +17858,43 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>3</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-15 12:07:37</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>21</v>
+      </c>
+      <c r="F38" t="n">
+        <v>22</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-15 12:14:09</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>392</v>
-      </c>
-      <c r="I38" t="n">
-        <v>6.53</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:04:42</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:11:27</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>405</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6.75</v>
       </c>
     </row>
     <row r="39">
@@ -17597,35 +17903,43 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>19</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-15 12:22:26</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16</v>
+      </c>
+      <c r="F39" t="n">
+        <v>17</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-15 12:29:14</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>408</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6.8</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:34:20</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:42:17</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>477</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7.95</v>
       </c>
     </row>
     <row r="40">
@@ -17634,35 +17948,43 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>7</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-15 12:50:59</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" t="n">
+        <v>17</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-15 12:56:05</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>306</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5.1</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:40:29</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:47:08</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>399</v>
+      </c>
+      <c r="K40" t="n">
+        <v>6.65</v>
       </c>
     </row>
     <row r="41">
@@ -17671,35 +17993,43 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>15</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D41" t="n">
-        <v>16</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-15 13:10:15</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>21</v>
+      </c>
+      <c r="F41" t="n">
+        <v>22</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-15 13:15:22</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>307</v>
-      </c>
-      <c r="I41" t="n">
-        <v>5.12</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:02:34</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:07:28</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>294</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="42">
@@ -17708,35 +18038,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>11</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-15 13:24:42</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" t="n">
+        <v>17</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-15 13:31:27</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>405</v>
-      </c>
-      <c r="I42" t="n">
-        <v>6.75</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:24:59</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:30:28</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>329</v>
+      </c>
+      <c r="K42" t="n">
+        <v>5.48</v>
       </c>
     </row>
     <row r="43">
@@ -17745,35 +18083,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-15 13:54:20</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>18</v>
+      </c>
+      <c r="F43" t="n">
+        <v>19</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-15 14:02:17</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>477</v>
-      </c>
-      <c r="I43" t="n">
-        <v>7.95</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:47:23</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:52:35</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>312</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.2</v>
       </c>
     </row>
     <row r="44">
@@ -17782,35 +18128,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>19</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:00:29</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F44" t="n">
+        <v>22</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-15 14:07:08</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>399</v>
-      </c>
-      <c r="I44" t="n">
-        <v>6.65</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:14:53</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:21:12</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>379</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6.32</v>
       </c>
     </row>
     <row r="45">
@@ -17819,35 +18173,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>7</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:23:04</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-15 14:29:21</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>377</v>
-      </c>
-      <c r="I45" t="n">
-        <v>6.28</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:20:42</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:28:11</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>449</v>
+      </c>
+      <c r="K45" t="n">
+        <v>7.48</v>
       </c>
     </row>
     <row r="46">
@@ -17856,35 +18218,43 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>11</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-15 14:48:08</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-15 14:56:06</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>478</v>
-      </c>
-      <c r="I46" t="n">
-        <v>7.97</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:43:56</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-15 14:48:30</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>274</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4.57</v>
       </c>
     </row>
     <row r="47">
@@ -17893,35 +18263,43 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>11</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D47" t="n">
-        <v>12</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:02:56</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18</v>
+      </c>
+      <c r="F47" t="n">
+        <v>19</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-15 15:07:58</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>302</v>
-      </c>
-      <c r="I47" t="n">
-        <v>5.03</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:03:56</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:08:23</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>267</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.45</v>
       </c>
     </row>
     <row r="48">
@@ -17930,35 +18308,43 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>19</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D48" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E48" t="n">
         <v>20</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:29:10</t>
-        </is>
+      <c r="F48" t="n">
+        <v>21</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-15 15:35:02</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>352</v>
-      </c>
-      <c r="I48" t="n">
-        <v>5.87</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:28:18</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:34:52</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>394</v>
+      </c>
+      <c r="K48" t="n">
+        <v>6.57</v>
       </c>
     </row>
     <row r="49">
@@ -17967,35 +18353,43 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E49" t="n">
         <v>21</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>22</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>STA_U - STA_V</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:49:39</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-09-15 15:57:05</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>446</v>
-      </c>
-      <c r="I49" t="n">
-        <v>7.43</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:50:13</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-15 15:57:08</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>415</v>
+      </c>
+      <c r="K49" t="n">
+        <v>6.92</v>
       </c>
     </row>
     <row r="50">
@@ -18004,35 +18398,43 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>19</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:00:42</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E50" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" t="n">
+        <v>16</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-15 16:08:11</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>449</v>
-      </c>
-      <c r="I50" t="n">
-        <v>7.48</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:15:16</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:23:07</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>471</v>
+      </c>
+      <c r="K50" t="n">
+        <v>7.85</v>
       </c>
     </row>
     <row r="51">
@@ -18041,35 +18443,43 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:29:59</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>21</v>
+      </c>
+      <c r="F51" t="n">
+        <v>22</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-15 16:36:48</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>409</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6.82</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:22:40</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:28:28</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>348</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="52">
@@ -18078,35 +18488,43 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-09-15 16:44:16</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E52" t="n">
+        <v>18</v>
+      </c>
+      <c r="F52" t="n">
+        <v>19</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-15 16:48:45</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>269</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4.48</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:41:00</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-15 16:46:25</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>325</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5.42</v>
       </c>
     </row>
     <row r="53">
@@ -18115,35 +18533,43 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>19</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:04:17</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E53" t="n">
+        <v>26</v>
+      </c>
+      <c r="F53" t="n">
+        <v>26</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-15 17:09:29</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>312</v>
-      </c>
-      <c r="I53" t="n">
-        <v>5.2</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:08:10</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:15:19</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>429</v>
+      </c>
+      <c r="K53" t="n">
+        <v>7.15</v>
       </c>
     </row>
     <row r="54">
@@ -18152,35 +18578,43 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>7</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:26:45</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16</v>
+      </c>
+      <c r="F54" t="n">
+        <v>17</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-15 17:32:12</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>327</v>
-      </c>
-      <c r="I54" t="n">
-        <v>5.45</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:33:35</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:37:37</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>242</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.03</v>
       </c>
     </row>
     <row r="55">
@@ -18189,35 +18623,43 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>11</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-09-15 17:48:32</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>18</v>
+      </c>
+      <c r="F55" t="n">
+        <v>19</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-09-15 17:54:37</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>365</v>
-      </c>
-      <c r="I55" t="n">
-        <v>6.08</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:42:56</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-15 17:49:52</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>416</v>
+      </c>
+      <c r="K55" t="n">
+        <v>6.93</v>
       </c>
     </row>
     <row r="56">
@@ -18226,35 +18668,43 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>15</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-09-15 18:01:05</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" t="n">
+        <v>19</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-09-15 18:07:47</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>402</v>
-      </c>
-      <c r="I56" t="n">
-        <v>6.7</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:01:53</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:07:27</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>334</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5.57</v>
       </c>
     </row>
     <row r="57">
@@ -18263,35 +18713,43 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>11</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D57" t="n">
-        <v>12</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-09-15 18:28:02</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>21</v>
+      </c>
+      <c r="F57" t="n">
+        <v>22</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-09-15 18:32:02</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>240</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:33:08</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:37:18</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>250</v>
+      </c>
+      <c r="K57" t="n">
+        <v>4.17</v>
       </c>
     </row>
     <row r="58">
@@ -18300,35 +18758,43 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>7</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D58" t="n">
-        <v>8</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-09-15 18:44:40</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>15</v>
+      </c>
+      <c r="F58" t="n">
+        <v>16</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-09-15 18:49:47</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>307</v>
-      </c>
-      <c r="I58" t="n">
-        <v>5.12</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:51:57</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-15 18:59:55</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>478</v>
+      </c>
+      <c r="K58" t="n">
+        <v>7.97</v>
       </c>
     </row>
     <row r="59">
@@ -18337,35 +18803,43 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>15</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-15 19:14:35</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20</v>
+      </c>
+      <c r="F59" t="n">
+        <v>21</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-09-15 19:21:35</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>420</v>
-      </c>
-      <c r="I59" t="n">
-        <v>7</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:11:13</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:18:07</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>414</v>
+      </c>
+      <c r="K59" t="n">
+        <v>6.9</v>
       </c>
     </row>
     <row r="60">
@@ -18374,35 +18848,43 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>21</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D60" t="n">
-        <v>22</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-15 19:20:07</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>25</v>
+      </c>
+      <c r="F60" t="n">
+        <v>26</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-09-15 19:24:26</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>259</v>
-      </c>
-      <c r="I60" t="n">
-        <v>4.32</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:23:22</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:30:41</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>439</v>
+      </c>
+      <c r="K60" t="n">
+        <v>7.32</v>
       </c>
     </row>
     <row r="61">
@@ -18411,35 +18893,43 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LC-03</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>11</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D61" t="n">
-        <v>12</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>STA_K - STA_L</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-09-15 19:44:34</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>20</v>
+      </c>
+      <c r="F61" t="n">
+        <v>21</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-09-15 19:48:43</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>249</v>
-      </c>
-      <c r="I61" t="n">
-        <v>4.15</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:44:59</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-15 19:52:57</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>478</v>
+      </c>
+      <c r="K61" t="n">
+        <v>7.97</v>
       </c>
     </row>
     <row r="62">
@@ -18448,35 +18938,43 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3</v>
+          <t>LC-33</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Perungalathur (Peerkankaranai)</t>
+        </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-09-15 20:04:27</t>
-        </is>
+        <v>32.2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>18</v>
+      </c>
+      <c r="F62" t="n">
+        <v>19</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-09-15 20:08:59</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>272</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4.53</v>
+          <t>STA_R - STA_S</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:05:51</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:13:18</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>447</v>
+      </c>
+      <c r="K62" t="n">
+        <v>7.45</v>
       </c>
     </row>
     <row r="63">
@@ -18485,35 +18983,43 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3</v>
+          <t>LC-52</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Potheri (SRM University Link)</t>
+        </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-09-15 20:29:23</t>
-        </is>
+        <v>44.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>23</v>
+      </c>
+      <c r="F63" t="n">
+        <v>24</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-09-15 20:37:13</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>470</v>
-      </c>
-      <c r="I63" t="n">
-        <v>7.83</v>
+          <t>STA_W - STA_X</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:33:01</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:37:46</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>285</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="64">
@@ -18522,35 +19028,43 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>7</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D64" t="n">
-        <v>8</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-09-15 20:51:13</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+      <c r="F64" t="n">
+        <v>21</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-09-15 20:58:07</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>414</v>
-      </c>
-      <c r="I64" t="n">
-        <v>6.9</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-09-15 20:53:51</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:00:42</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>411</v>
+      </c>
+      <c r="K64" t="n">
+        <v>6.85</v>
       </c>
     </row>
     <row r="65">
@@ -18559,35 +19073,43 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LC-05</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>19</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>STA_S - STA_T</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:03:22</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E65" t="n">
+        <v>16</v>
+      </c>
+      <c r="F65" t="n">
+        <v>17</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-09-15 21:10:41</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>439</v>
-      </c>
-      <c r="I65" t="n">
-        <v>7.32</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:08:10</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:15:31</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>441</v>
+      </c>
+      <c r="K65" t="n">
+        <v>7.35</v>
       </c>
     </row>
     <row r="66">
@@ -18596,35 +19118,43 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>7</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:33:39</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>26</v>
+      </c>
+      <c r="F66" t="n">
+        <v>26</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-09-15 21:40:50</t>
-        </is>
-      </c>
-      <c r="H66" t="n">
-        <v>431</v>
-      </c>
-      <c r="I66" t="n">
-        <v>7.18</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:32:55</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:37:04</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>249</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4.15</v>
       </c>
     </row>
     <row r="67">
@@ -18633,35 +19163,43 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>7</v>
+          <t>LC-61</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Paranur (Mahindra World City)</t>
+        </is>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-09-15 21:47:55</t>
-        </is>
+        <v>56.4</v>
+      </c>
+      <c r="E67" t="n">
+        <v>26</v>
+      </c>
+      <c r="F67" t="n">
+        <v>26</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-09-15 21:52:36</t>
-        </is>
-      </c>
-      <c r="H67" t="n">
-        <v>281</v>
-      </c>
-      <c r="I67" t="n">
-        <v>4.68</v>
+          <t>STA_Z - STA_Z</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:47:12</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-15 21:54:41</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>449</v>
+      </c>
+      <c r="K67" t="n">
+        <v>7.48</v>
       </c>
     </row>
     <row r="68">
@@ -18670,35 +19208,43 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="E68" t="n">
+        <v>20</v>
+      </c>
+      <c r="F68" t="n">
         <v>21</v>
       </c>
-      <c r="D68" t="n">
-        <v>22</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-09-15 22:13:01</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-09-15 22:17:46</t>
-        </is>
-      </c>
-      <c r="H68" t="n">
-        <v>285</v>
-      </c>
-      <c r="I68" t="n">
-        <v>4.75</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:11:19</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:18:49</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>450</v>
+      </c>
+      <c r="K68" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="69">
@@ -18707,35 +19253,43 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>15</v>
+          <t>LC-43</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vandalur - Urapakkam (Otteri)</t>
+        </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-09-15 22:30:50</t>
-        </is>
+        <v>36.8</v>
+      </c>
+      <c r="E69" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" t="n">
+        <v>21</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-09-15 22:38:48</t>
-        </is>
-      </c>
-      <c r="H69" t="n">
-        <v>478</v>
-      </c>
-      <c r="I69" t="n">
-        <v>7.97</v>
+          <t>STA_T - STA_U</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:27:01</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:33:49</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>408</v>
+      </c>
+      <c r="K69" t="n">
+        <v>6.8</v>
       </c>
     </row>
     <row r="70">
@@ -18744,35 +19298,43 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LC-06</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>21</v>
+          <t>LC-27</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Chromepet (MIT Gate)</t>
+        </is>
       </c>
       <c r="D70" t="n">
-        <v>22</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>STA_U - STA_V</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-09-15 22:47:17</t>
-        </is>
+        <v>25.8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16</v>
+      </c>
+      <c r="F70" t="n">
+        <v>17</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-09-15 22:51:57</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
-        <v>280</v>
-      </c>
-      <c r="I70" t="n">
-        <v>4.67</v>
+          <t>STA_P - STA_Q</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:52:21</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:57:32</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>311</v>
+      </c>
+      <c r="K70" t="n">
+        <v>5.18</v>
       </c>
     </row>
     <row r="71">
@@ -18781,35 +19343,43 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LC-01</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>3</v>
+          <t>LC-58</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Singaperumal Koil (Temple Gate)</t>
+        </is>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>STA_C - STA_D</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-09-15 23:03:24</t>
-        </is>
+        <v>52.3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" t="n">
+        <v>26</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-09-15 23:11:07</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>463</v>
-      </c>
-      <c r="I71" t="n">
-        <v>7.72</v>
+          <t>STA_Y - STA_Z</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:08:22</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:15:06</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>404</v>
+      </c>
+      <c r="K71" t="n">
+        <v>6.73</v>
       </c>
     </row>
     <row r="72">
@@ -18818,35 +19388,43 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LC-04</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>15</v>
+          <t>LC-47</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Guduvancheri (Market Road)</t>
+        </is>
       </c>
       <c r="D72" t="n">
-        <v>16</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>STA_O - STA_P</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-09-15 23:35:14</t>
-        </is>
+        <v>41.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>21</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-09-15 23:40:05</t>
-        </is>
-      </c>
-      <c r="H72" t="n">
-        <v>291</v>
-      </c>
-      <c r="I72" t="n">
-        <v>4.85</v>
+          <t>STA_U - STA_V</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:30:01</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:34:30</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>269</v>
+      </c>
+      <c r="K72" t="n">
+        <v>4.48</v>
       </c>
     </row>
     <row r="73">
@@ -18855,35 +19433,43 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LC-02</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>7</v>
+          <t>LC-26</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chromepet (Radha Nagar)</t>
+        </is>
       </c>
       <c r="D73" t="n">
-        <v>8</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>STA_G - STA_H</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-09-15 23:51:19</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E73" t="n">
+        <v>15</v>
+      </c>
+      <c r="F73" t="n">
+        <v>16</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-09-15 23:58:49</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>450</v>
-      </c>
-      <c r="I73" t="n">
-        <v>7.5</v>
+          <t>STA_O - STA_P</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:45:37</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-15 23:50:44</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>307</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5.12</v>
       </c>
     </row>
   </sheetData>
